--- a/reports/Debug-purgatory-20260111/Month to Date (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260111/Month to Date (Prior Year)_Revenue.xlsx
@@ -109,19 +109,19 @@
     <t>T103</t>
   </si>
   <si>
+    <t>T110</t>
+  </si>
+  <si>
+    <t>T101</t>
+  </si>
+  <si>
+    <t>T105</t>
+  </si>
+  <si>
     <t>T104</t>
   </si>
   <si>
-    <t>T105</t>
-  </si>
-  <si>
-    <t>T110</t>
-  </si>
-  <si>
     <t>T100</t>
-  </si>
-  <si>
-    <t>T101</t>
   </si>
   <si>
     <t>department</t>
@@ -622,7 +622,7 @@
         <v>37</v>
       </c>
       <c r="D3" s="2">
-        <v>69.50</v>
+        <v>240.00</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -636,7 +636,7 @@
         <v>37</v>
       </c>
       <c r="D4" s="2">
-        <v>5626.00</v>
+        <v>10391.72</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -650,7 +650,7 @@
         <v>37</v>
       </c>
       <c r="D5" s="2">
-        <v>240.00</v>
+        <v>5626.00</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -664,7 +664,7 @@
         <v>37</v>
       </c>
       <c r="D6" s="2">
-        <v>665524.68</v>
+        <v>69.50</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -678,7 +678,7 @@
         <v>37</v>
       </c>
       <c r="D7" s="2">
-        <v>10391.72</v>
+        <v>665524.68</v>
       </c>
     </row>
     <row r="8" spans="1:4">
